--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256543C0-04A6-4D05-A7C2-7EE0687CBC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D8E106-F83A-4805-8EF6-C5880B450618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24090" yWindow="6420" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="131">
   <si>
     <t>Mammoth</t>
   </si>
@@ -522,8 +522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V127" totalsRowShown="0">
-  <autoFilter ref="A1:V127" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V139" totalsRowShown="0">
+  <autoFilter ref="A1:V139" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
     <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
@@ -590,8 +590,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}" name="Table2" displayName="Table2" ref="A1:D323" totalsRowShown="0">
-  <autoFilter ref="A1:D323" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}" name="Table2" displayName="Table2" ref="A1:D415" totalsRowShown="0">
+  <autoFilter ref="A1:D415" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E9D80D2D-BB1D-4FDE-90CE-06D854D914ED}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{84AE994F-16AA-4683-9C1D-6B8C3F098F6A}" name="Parent"/>
@@ -900,7 +900,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W127"/>
+  <dimension ref="A1:W139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -10734,7 +10734,7 @@
         <v>446</v>
       </c>
       <c r="E125" s="3">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="F125">
         <v>39</v>
@@ -10759,19 +10759,19 @@
       </c>
       <c r="M125" s="4">
         <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
-        <v>1</v>
+        <v>0.19024390243902439</v>
       </c>
       <c r="N125" s="4">
         <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
-        <v>7.6923076923076927E-2</v>
+        <v>1.4634146341463415E-2</v>
       </c>
       <c r="O125" s="4">
         <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
-        <v>5.128205128205128E-2</v>
+        <v>9.7560975609756097E-3</v>
       </c>
       <c r="P125" s="4">
         <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>8.744394618834081E-2</v>
+        <v>0.45964125560538116</v>
       </c>
       <c r="Q125" s="4">
         <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
@@ -10787,15 +10787,15 @@
       </c>
       <c r="T125" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="U125" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>0.30044843049327352</v>
+        <v>0.67264573991031396</v>
       </c>
       <c r="V125" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
-        <v>3.4358974358974357</v>
+        <v>1.4634146341463414</v>
       </c>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
@@ -10956,8 +10956,956 @@
         <v>2.1111111111111112</v>
       </c>
     </row>
+    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B128" t="s">
+        <v>0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D128" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>483</v>
+      </c>
+      <c r="E128" s="3">
+        <v>954</v>
+      </c>
+      <c r="F128">
+        <v>225</v>
+      </c>
+      <c r="G128">
+        <v>14</v>
+      </c>
+      <c r="H128">
+        <v>6</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.23584905660377359</v>
+      </c>
+      <c r="N128" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4675052410901468E-2</v>
+      </c>
+      <c r="O128" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.2893081761006293E-3</v>
+      </c>
+      <c r="P128" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.9751552795031055</v>
+      </c>
+      <c r="Q128" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.46583850931677018</v>
+      </c>
+      <c r="R128" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8985507246376812E-2</v>
+      </c>
+      <c r="S128" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2422360248447204E-2</v>
+      </c>
+      <c r="T128" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1470</v>
+      </c>
+      <c r="U128" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0434782608695654</v>
+      </c>
+      <c r="V128" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5408805031446542</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D129" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>482</v>
+      </c>
+      <c r="E129" s="3">
+        <v>478</v>
+      </c>
+      <c r="F129">
+        <v>144</v>
+      </c>
+      <c r="G129">
+        <v>8</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.30125523012552302</v>
+      </c>
+      <c r="N129" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6736401673640166E-2</v>
+      </c>
+      <c r="O129" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0920502092050207E-3</v>
+      </c>
+      <c r="P129" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.99170124481327804</v>
+      </c>
+      <c r="Q129" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.29875518672199169</v>
+      </c>
+      <c r="R129" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6597510373443983E-2</v>
+      </c>
+      <c r="S129" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.0746887966804979E-3</v>
+      </c>
+      <c r="T129" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>794</v>
+      </c>
+      <c r="U129" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6473029045643153</v>
+      </c>
+      <c r="V129" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6610878661087867</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D130" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>337</v>
+      </c>
+      <c r="E130" s="3">
+        <v>519</v>
+      </c>
+      <c r="F130">
+        <v>264</v>
+      </c>
+      <c r="G130">
+        <v>9</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.50867052023121384</v>
+      </c>
+      <c r="N130" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7341040462427744E-2</v>
+      </c>
+      <c r="O130" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9267822736030828E-3</v>
+      </c>
+      <c r="P130" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5400593471810089</v>
+      </c>
+      <c r="Q130" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.78338278931750738</v>
+      </c>
+      <c r="R130" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.6706231454005934E-2</v>
+      </c>
+      <c r="S130" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.967359050445104E-3</v>
+      </c>
+      <c r="T130" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1078</v>
+      </c>
+      <c r="U130" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1988130563798221</v>
+      </c>
+      <c r="V130" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0770712909441231</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B131" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D131" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>517</v>
+      </c>
+      <c r="E131" s="3">
+        <v>208</v>
+      </c>
+      <c r="F131">
+        <v>41</v>
+      </c>
+      <c r="G131">
+        <v>3</v>
+      </c>
+      <c r="H131">
+        <v>2</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19711538461538461</v>
+      </c>
+      <c r="N131" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4423076923076924E-2</v>
+      </c>
+      <c r="O131" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>9.6153846153846159E-3</v>
+      </c>
+      <c r="P131" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.40232108317214699</v>
+      </c>
+      <c r="Q131" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>7.9303675048355893E-2</v>
+      </c>
+      <c r="R131" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>5.8027079303675051E-3</v>
+      </c>
+      <c r="S131" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.8684719535783366E-3</v>
+      </c>
+      <c r="T131" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>307</v>
+      </c>
+      <c r="U131" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.5938104448742747</v>
+      </c>
+      <c r="V131" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4759615384615385</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B132" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D132" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>335</v>
+      </c>
+      <c r="E132" s="3">
+        <v>296</v>
+      </c>
+      <c r="F132">
+        <v>31</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.10472972972972973</v>
+      </c>
+      <c r="N132" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>3.3783783783783786E-3</v>
+      </c>
+      <c r="O132" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>3.3783783783783786E-3</v>
+      </c>
+      <c r="P132" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.88358208955223883</v>
+      </c>
+      <c r="Q132" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.2537313432835819E-2</v>
+      </c>
+      <c r="R132" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9850746268656717E-3</v>
+      </c>
+      <c r="S132" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9850746268656717E-3</v>
+      </c>
+      <c r="T132" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>365</v>
+      </c>
+      <c r="U132" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0895522388059702</v>
+      </c>
+      <c r="V132" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2331081081081081</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D133" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>233</v>
+      </c>
+      <c r="E133" s="3">
+        <v>179</v>
+      </c>
+      <c r="F133">
+        <v>104</v>
+      </c>
+      <c r="G133">
+        <v>2</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.58100558659217882</v>
+      </c>
+      <c r="N133" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.11731843575419E-2</v>
+      </c>
+      <c r="O133" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P133" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.76824034334763946</v>
+      </c>
+      <c r="Q133" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.44635193133047213</v>
+      </c>
+      <c r="R133" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>8.5836909871244635E-3</v>
+      </c>
+      <c r="S133" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T133" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>393</v>
+      </c>
+      <c r="U133" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6866952789699572</v>
+      </c>
+      <c r="V133" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1955307262569832</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B134" t="s">
+        <v>0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D134" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>490</v>
+      </c>
+      <c r="E134" s="3">
+        <v>960</v>
+      </c>
+      <c r="F134">
+        <v>225</v>
+      </c>
+      <c r="G134">
+        <v>14</v>
+      </c>
+      <c r="H134">
+        <v>6</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.234375</v>
+      </c>
+      <c r="N134" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4583333333333334E-2</v>
+      </c>
+      <c r="O134" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="P134" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.9591836734693877</v>
+      </c>
+      <c r="Q134" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.45918367346938777</v>
+      </c>
+      <c r="R134" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8571428571428571E-2</v>
+      </c>
+      <c r="S134" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2244897959183673E-2</v>
+      </c>
+      <c r="T134" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1476</v>
+      </c>
+      <c r="U134" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0122448979591838</v>
+      </c>
+      <c r="V134" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5375000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1</v>
+      </c>
+      <c r="C135" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D135" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>489</v>
+      </c>
+      <c r="E135" s="3">
+        <v>483</v>
+      </c>
+      <c r="F135">
+        <v>144</v>
+      </c>
+      <c r="G135">
+        <v>8</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29813664596273293</v>
+      </c>
+      <c r="N135" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6563146997929608E-2</v>
+      </c>
+      <c r="O135" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.070393374741201E-3</v>
+      </c>
+      <c r="P135" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.98773006134969321</v>
+      </c>
+      <c r="Q135" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.29447852760736198</v>
+      </c>
+      <c r="R135" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6359918200408999E-2</v>
+      </c>
+      <c r="S135" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.0449897750511249E-3</v>
+      </c>
+      <c r="T135" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>799</v>
+      </c>
+      <c r="U135" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6339468302658486</v>
+      </c>
+      <c r="V135" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6542443064182195</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B136" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D136" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>344</v>
+      </c>
+      <c r="E136" s="3">
+        <v>535</v>
+      </c>
+      <c r="F136">
+        <v>265</v>
+      </c>
+      <c r="G136">
+        <v>9</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.49532710280373832</v>
+      </c>
+      <c r="N136" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6822429906542057E-2</v>
+      </c>
+      <c r="O136" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.869158878504673E-3</v>
+      </c>
+      <c r="P136" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.555232558139535</v>
+      </c>
+      <c r="Q136" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.77034883720930236</v>
+      </c>
+      <c r="R136" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.616279069767442E-2</v>
+      </c>
+      <c r="S136" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9069767441860465E-3</v>
+      </c>
+      <c r="T136" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1096</v>
+      </c>
+      <c r="U136" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1860465116279069</v>
+      </c>
+      <c r="V136" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0485981308411216</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D137" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>524</v>
+      </c>
+      <c r="E137" s="3">
+        <v>214</v>
+      </c>
+      <c r="F137">
+        <v>42</v>
+      </c>
+      <c r="G137">
+        <v>3</v>
+      </c>
+      <c r="H137">
+        <v>2</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19626168224299065</v>
+      </c>
+      <c r="N137" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4018691588785047E-2</v>
+      </c>
+      <c r="O137" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>9.3457943925233638E-3</v>
+      </c>
+      <c r="P137" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.40839694656488551</v>
+      </c>
+      <c r="Q137" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.0152671755725186E-2</v>
+      </c>
+      <c r="R137" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>5.7251908396946565E-3</v>
+      </c>
+      <c r="S137" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.8167938931297708E-3</v>
+      </c>
+      <c r="T137" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>315</v>
+      </c>
+      <c r="U137" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.60114503816793896</v>
+      </c>
+      <c r="V137" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.47196261682243</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B138" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D138" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>342</v>
+      </c>
+      <c r="E138" s="3">
+        <v>303</v>
+      </c>
+      <c r="F138">
+        <v>32</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.10561056105610561</v>
+      </c>
+      <c r="N138" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>3.3003300330033004E-3</v>
+      </c>
+      <c r="O138" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>3.3003300330033004E-3</v>
+      </c>
+      <c r="P138" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.88596491228070173</v>
+      </c>
+      <c r="Q138" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.3567251461988299E-2</v>
+      </c>
+      <c r="R138" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9239766081871343E-3</v>
+      </c>
+      <c r="S138" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9239766081871343E-3</v>
+      </c>
+      <c r="T138" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>374</v>
+      </c>
+      <c r="U138" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0935672514619883</v>
+      </c>
+      <c r="V138" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2343234323432344</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D139" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>240</v>
+      </c>
+      <c r="E139" s="3">
+        <v>184</v>
+      </c>
+      <c r="F139">
+        <v>105</v>
+      </c>
+      <c r="G139">
+        <v>3</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.57065217391304346</v>
+      </c>
+      <c r="N139" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6304347826086956E-2</v>
+      </c>
+      <c r="O139" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P139" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="Q139" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.4375</v>
+      </c>
+      <c r="R139" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="S139" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T139" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>403</v>
+      </c>
+      <c r="U139" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6791666666666667</v>
+      </c>
+      <c r="V139" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1902173913043477</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C127">
+  <conditionalFormatting sqref="C2:C139">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10969,7 +11917,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C98:C127">
+  <conditionalFormatting sqref="C98:C139">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -11005,7 +11953,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F127">
+  <conditionalFormatting sqref="F2:F139">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11029,7 +11977,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G127">
+  <conditionalFormatting sqref="G2:G139">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11053,7 +12001,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H127">
+  <conditionalFormatting sqref="H1:H139">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -11087,7 +12035,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N127">
+  <conditionalFormatting sqref="N2:N139">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -11111,7 +12059,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O127">
+  <conditionalFormatting sqref="O2:O139">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -11135,7 +12083,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P127">
+  <conditionalFormatting sqref="P2:P139">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -11159,7 +12107,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q127">
+  <conditionalFormatting sqref="Q2:Q139">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -11171,7 +12119,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R127">
+  <conditionalFormatting sqref="R2:R139">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -11195,7 +12143,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S127">
+  <conditionalFormatting sqref="S2:S139">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -11219,7 +12167,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T127">
+  <conditionalFormatting sqref="T2:T139">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -11243,7 +12191,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U127">
+  <conditionalFormatting sqref="U2:U139">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -11279,7 +12227,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V127">
+  <conditionalFormatting sqref="W8:W1048576 V1:V139">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -12263,7 +13211,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC82DCFF-7BE9-4E03-A7FB-F5958C6B535A}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D323"/>
+  <dimension ref="A1:D415"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -16794,6 +17742,1294 @@
         <v>10</v>
       </c>
     </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B324" t="s">
+        <v>0</v>
+      </c>
+      <c r="C324" t="s">
+        <v>32</v>
+      </c>
+      <c r="D324">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1</v>
+      </c>
+      <c r="C325" t="s">
+        <v>34</v>
+      </c>
+      <c r="D325">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1</v>
+      </c>
+      <c r="C326" t="s">
+        <v>36</v>
+      </c>
+      <c r="D326">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B327" t="s">
+        <v>1</v>
+      </c>
+      <c r="C327" t="s">
+        <v>38</v>
+      </c>
+      <c r="D327">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1</v>
+      </c>
+      <c r="C328" t="s">
+        <v>40</v>
+      </c>
+      <c r="D328">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B329" t="s">
+        <v>1</v>
+      </c>
+      <c r="C329" t="s">
+        <v>42</v>
+      </c>
+      <c r="D329">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B330" t="s">
+        <v>1</v>
+      </c>
+      <c r="C330" t="s">
+        <v>44</v>
+      </c>
+      <c r="D330">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1</v>
+      </c>
+      <c r="C331" t="s">
+        <v>46</v>
+      </c>
+      <c r="D331">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1</v>
+      </c>
+      <c r="C332" t="s">
+        <v>48</v>
+      </c>
+      <c r="D332">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1</v>
+      </c>
+      <c r="C333" t="s">
+        <v>50</v>
+      </c>
+      <c r="D333">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B334" t="s">
+        <v>2</v>
+      </c>
+      <c r="C334" t="s">
+        <v>52</v>
+      </c>
+      <c r="D334">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B335" t="s">
+        <v>2</v>
+      </c>
+      <c r="C335" t="s">
+        <v>54</v>
+      </c>
+      <c r="D335">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B336" t="s">
+        <v>2</v>
+      </c>
+      <c r="C336" t="s">
+        <v>56</v>
+      </c>
+      <c r="D336">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B337" t="s">
+        <v>2</v>
+      </c>
+      <c r="C337" t="s">
+        <v>58</v>
+      </c>
+      <c r="D337">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B338" t="s">
+        <v>2</v>
+      </c>
+      <c r="C338" t="s">
+        <v>60</v>
+      </c>
+      <c r="D338">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B339" t="s">
+        <v>2</v>
+      </c>
+      <c r="C339" t="s">
+        <v>62</v>
+      </c>
+      <c r="D339">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B340" t="s">
+        <v>2</v>
+      </c>
+      <c r="C340" t="s">
+        <v>64</v>
+      </c>
+      <c r="D340">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B341" t="s">
+        <v>2</v>
+      </c>
+      <c r="C341" t="s">
+        <v>66</v>
+      </c>
+      <c r="D341">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B342" t="s">
+        <v>2</v>
+      </c>
+      <c r="C342" t="s">
+        <v>68</v>
+      </c>
+      <c r="D342">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B343" t="s">
+        <v>2</v>
+      </c>
+      <c r="C343" t="s">
+        <v>70</v>
+      </c>
+      <c r="D343">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B344" t="s">
+        <v>2</v>
+      </c>
+      <c r="C344" t="s">
+        <v>72</v>
+      </c>
+      <c r="D344">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B345" t="s">
+        <v>2</v>
+      </c>
+      <c r="C345" t="s">
+        <v>74</v>
+      </c>
+      <c r="D345">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B346" t="s">
+        <v>2</v>
+      </c>
+      <c r="C346" t="s">
+        <v>76</v>
+      </c>
+      <c r="D346">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B347" t="s">
+        <v>2</v>
+      </c>
+      <c r="C347" t="s">
+        <v>78</v>
+      </c>
+      <c r="D347">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B348" t="s">
+        <v>2</v>
+      </c>
+      <c r="C348" t="s">
+        <v>80</v>
+      </c>
+      <c r="D348">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B349" t="s">
+        <v>13</v>
+      </c>
+      <c r="C349" t="s">
+        <v>82</v>
+      </c>
+      <c r="D349">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B350" t="s">
+        <v>3</v>
+      </c>
+      <c r="C350" t="s">
+        <v>84</v>
+      </c>
+      <c r="D350">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B351" t="s">
+        <v>4</v>
+      </c>
+      <c r="C351" t="s">
+        <v>86</v>
+      </c>
+      <c r="D351">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B352" t="s">
+        <v>4</v>
+      </c>
+      <c r="C352" t="s">
+        <v>88</v>
+      </c>
+      <c r="D352">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B353" t="s">
+        <v>4</v>
+      </c>
+      <c r="C353" t="s">
+        <v>90</v>
+      </c>
+      <c r="D353">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B354" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" t="s">
+        <v>92</v>
+      </c>
+      <c r="D354">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B355" t="s">
+        <v>4</v>
+      </c>
+      <c r="C355" t="s">
+        <v>94</v>
+      </c>
+      <c r="D355">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B356" t="s">
+        <v>4</v>
+      </c>
+      <c r="C356" t="s">
+        <v>96</v>
+      </c>
+      <c r="D356">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B357" t="s">
+        <v>4</v>
+      </c>
+      <c r="C357" t="s">
+        <v>98</v>
+      </c>
+      <c r="D357">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B358" t="s">
+        <v>4</v>
+      </c>
+      <c r="C358" t="s">
+        <v>100</v>
+      </c>
+      <c r="D358">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B359" t="s">
+        <v>4</v>
+      </c>
+      <c r="C359" t="s">
+        <v>102</v>
+      </c>
+      <c r="D359">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B360" t="s">
+        <v>4</v>
+      </c>
+      <c r="C360" t="s">
+        <v>104</v>
+      </c>
+      <c r="D360">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B361" t="s">
+        <v>4</v>
+      </c>
+      <c r="C361" t="s">
+        <v>106</v>
+      </c>
+      <c r="D361">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B362" t="s">
+        <v>4</v>
+      </c>
+      <c r="C362" t="s">
+        <v>108</v>
+      </c>
+      <c r="D362">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B363" t="s">
+        <v>4</v>
+      </c>
+      <c r="C363" t="s">
+        <v>110</v>
+      </c>
+      <c r="D363">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B364" t="s">
+        <v>4</v>
+      </c>
+      <c r="C364" t="s">
+        <v>112</v>
+      </c>
+      <c r="D364">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B365" t="s">
+        <v>4</v>
+      </c>
+      <c r="C365" t="s">
+        <v>114</v>
+      </c>
+      <c r="D365">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B366" t="s">
+        <v>4</v>
+      </c>
+      <c r="C366" t="s">
+        <v>116</v>
+      </c>
+      <c r="D366">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B367" t="s">
+        <v>4</v>
+      </c>
+      <c r="C367" t="s">
+        <v>118</v>
+      </c>
+      <c r="D367">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B368" t="s">
+        <v>4</v>
+      </c>
+      <c r="C368" t="s">
+        <v>120</v>
+      </c>
+      <c r="D368">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B369" t="s">
+        <v>4</v>
+      </c>
+      <c r="C369" t="s">
+        <v>122</v>
+      </c>
+      <c r="D369">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B370" t="s">
+        <v>0</v>
+      </c>
+      <c r="C370" t="s">
+        <v>32</v>
+      </c>
+      <c r="D370">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1</v>
+      </c>
+      <c r="C371" t="s">
+        <v>34</v>
+      </c>
+      <c r="D371">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1</v>
+      </c>
+      <c r="C372" t="s">
+        <v>36</v>
+      </c>
+      <c r="D372">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1</v>
+      </c>
+      <c r="C373" t="s">
+        <v>38</v>
+      </c>
+      <c r="D373">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1</v>
+      </c>
+      <c r="C374" t="s">
+        <v>40</v>
+      </c>
+      <c r="D374">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1</v>
+      </c>
+      <c r="C375" t="s">
+        <v>42</v>
+      </c>
+      <c r="D375">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1</v>
+      </c>
+      <c r="C376" t="s">
+        <v>44</v>
+      </c>
+      <c r="D376">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1</v>
+      </c>
+      <c r="C377" t="s">
+        <v>46</v>
+      </c>
+      <c r="D377">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1</v>
+      </c>
+      <c r="C378" t="s">
+        <v>48</v>
+      </c>
+      <c r="D378">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1</v>
+      </c>
+      <c r="C379" t="s">
+        <v>50</v>
+      </c>
+      <c r="D379">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B380" t="s">
+        <v>2</v>
+      </c>
+      <c r="C380" t="s">
+        <v>52</v>
+      </c>
+      <c r="D380">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B381" t="s">
+        <v>2</v>
+      </c>
+      <c r="C381" t="s">
+        <v>54</v>
+      </c>
+      <c r="D381">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B382" t="s">
+        <v>2</v>
+      </c>
+      <c r="C382" t="s">
+        <v>56</v>
+      </c>
+      <c r="D382">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B383" t="s">
+        <v>2</v>
+      </c>
+      <c r="C383" t="s">
+        <v>58</v>
+      </c>
+      <c r="D383">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B384" t="s">
+        <v>2</v>
+      </c>
+      <c r="C384" t="s">
+        <v>60</v>
+      </c>
+      <c r="D384">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B385" t="s">
+        <v>2</v>
+      </c>
+      <c r="C385" t="s">
+        <v>62</v>
+      </c>
+      <c r="D385">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B386" t="s">
+        <v>2</v>
+      </c>
+      <c r="C386" t="s">
+        <v>64</v>
+      </c>
+      <c r="D386">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B387" t="s">
+        <v>2</v>
+      </c>
+      <c r="C387" t="s">
+        <v>66</v>
+      </c>
+      <c r="D387">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B388" t="s">
+        <v>2</v>
+      </c>
+      <c r="C388" t="s">
+        <v>68</v>
+      </c>
+      <c r="D388">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B389" t="s">
+        <v>2</v>
+      </c>
+      <c r="C389" t="s">
+        <v>70</v>
+      </c>
+      <c r="D389">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B390" t="s">
+        <v>2</v>
+      </c>
+      <c r="C390" t="s">
+        <v>72</v>
+      </c>
+      <c r="D390">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B391" t="s">
+        <v>2</v>
+      </c>
+      <c r="C391" t="s">
+        <v>74</v>
+      </c>
+      <c r="D391">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B392" t="s">
+        <v>2</v>
+      </c>
+      <c r="C392" t="s">
+        <v>76</v>
+      </c>
+      <c r="D392">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B393" t="s">
+        <v>2</v>
+      </c>
+      <c r="C393" t="s">
+        <v>78</v>
+      </c>
+      <c r="D393">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B394" t="s">
+        <v>2</v>
+      </c>
+      <c r="C394" t="s">
+        <v>80</v>
+      </c>
+      <c r="D394">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B395" t="s">
+        <v>13</v>
+      </c>
+      <c r="C395" t="s">
+        <v>82</v>
+      </c>
+      <c r="D395">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B396" t="s">
+        <v>3</v>
+      </c>
+      <c r="C396" t="s">
+        <v>84</v>
+      </c>
+      <c r="D396">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B397" t="s">
+        <v>4</v>
+      </c>
+      <c r="C397" t="s">
+        <v>86</v>
+      </c>
+      <c r="D397">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B398" t="s">
+        <v>4</v>
+      </c>
+      <c r="C398" t="s">
+        <v>88</v>
+      </c>
+      <c r="D398">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B399" t="s">
+        <v>4</v>
+      </c>
+      <c r="C399" t="s">
+        <v>90</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B400" t="s">
+        <v>4</v>
+      </c>
+      <c r="C400" t="s">
+        <v>92</v>
+      </c>
+      <c r="D400">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B401" t="s">
+        <v>4</v>
+      </c>
+      <c r="C401" t="s">
+        <v>94</v>
+      </c>
+      <c r="D401">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B402" t="s">
+        <v>4</v>
+      </c>
+      <c r="C402" t="s">
+        <v>96</v>
+      </c>
+      <c r="D402">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B403" t="s">
+        <v>4</v>
+      </c>
+      <c r="C403" t="s">
+        <v>98</v>
+      </c>
+      <c r="D403">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B404" t="s">
+        <v>4</v>
+      </c>
+      <c r="C404" t="s">
+        <v>100</v>
+      </c>
+      <c r="D404">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B405" t="s">
+        <v>4</v>
+      </c>
+      <c r="C405" t="s">
+        <v>102</v>
+      </c>
+      <c r="D405">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B406" t="s">
+        <v>4</v>
+      </c>
+      <c r="C406" t="s">
+        <v>104</v>
+      </c>
+      <c r="D406">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B407" t="s">
+        <v>4</v>
+      </c>
+      <c r="C407" t="s">
+        <v>106</v>
+      </c>
+      <c r="D407">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B408" t="s">
+        <v>4</v>
+      </c>
+      <c r="C408" t="s">
+        <v>108</v>
+      </c>
+      <c r="D408">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B409" t="s">
+        <v>4</v>
+      </c>
+      <c r="C409" t="s">
+        <v>110</v>
+      </c>
+      <c r="D409">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B410" t="s">
+        <v>4</v>
+      </c>
+      <c r="C410" t="s">
+        <v>112</v>
+      </c>
+      <c r="D410">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B411" t="s">
+        <v>4</v>
+      </c>
+      <c r="C411" t="s">
+        <v>114</v>
+      </c>
+      <c r="D411">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B412" t="s">
+        <v>4</v>
+      </c>
+      <c r="C412" t="s">
+        <v>116</v>
+      </c>
+      <c r="D412">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B413" t="s">
+        <v>4</v>
+      </c>
+      <c r="C413" t="s">
+        <v>118</v>
+      </c>
+      <c r="D413">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B414" t="s">
+        <v>4</v>
+      </c>
+      <c r="C414" t="s">
+        <v>120</v>
+      </c>
+      <c r="D414">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B415" t="s">
+        <v>4</v>
+      </c>
+      <c r="C415" t="s">
+        <v>122</v>
+      </c>
+      <c r="D415">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
